--- a/data/vocab_sets.xlsx
+++ b/data/vocab_sets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,45 +466,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ID_20260324081028039774</t>
+          <t>ID_20260326173912109119</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>kiki</t>
+          <t>GEAGA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kekeke</t>
+          <t>AGSWAEADS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-24 08:10</t>
+          <t>2026-03-26 17:39</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27 10:56</t>
+          <t>2026-03-27 14:23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>just now</t>
+          <t>Never</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>hihi</t>
+          <t>HEEAH</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>jojojo</t>
+          <t>AWDASDAS</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-26 17:39</t>
+          <t>2026-03-27 14:23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -544,12 +544,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>HEEAH</t>
+          <t>AWGAWADSA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AWDASDAS</t>
+          <t>AWDWAE</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-26 17:39</t>
+          <t>2026-03-27 14:23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,29 +589,29 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AWGAWADSA</t>
+          <t>ADWDWAFAGWAWASZXV</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AWDWAE</t>
+          <t>SAFDSAFAWFAW</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ID_20260326173912109119</t>
+          <t>ID_20260326173946573279</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GEAGA</t>
+          <t>QWIJAJS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AGSWAEADS</t>
+          <t>ASCBJCASBJ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -634,12 +634,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ADWDWAFAGWAWASZXV</t>
+          <t>HMMM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SAFDSAFAWFAW</t>
+          <t>YEAHH</t>
         </is>
       </c>
     </row>
@@ -679,12 +679,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>HMMM</t>
+          <t>CUTECUTE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>YEAHH</t>
+          <t>YAMAAA</t>
         </is>
       </c>
     </row>
@@ -724,192 +724,102 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CUTECUTE</t>
+          <t>YOMOST</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>YAMAAA</t>
+          <t>HIHIHIHIASHUOHAS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ID_20260326173946573279</t>
+          <t>ID_20260327111429770448</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>QWIJAJS</t>
+          <t>asdasd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ASCBJCASBJ</t>
+          <t>asdasdsad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-26 17:39</t>
+          <t>2026-03-27 11:14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-03-26 17:39</t>
+          <t>2026-03-27 11:14</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>just now</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>YOMOST</t>
+          <t>asfasf</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HIHIHIHIASHUOHAS</t>
+          <t>afsafs</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ID_20260326174009525270</t>
+          <t>ID_20260327111429770448</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASDSADSA</t>
+          <t>asdasd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ASFFSAQWE</t>
+          <t>asdasdsad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-26 17:40</t>
+          <t>2026-03-27 11:14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-03-26 17:40</t>
+          <t>2026-03-27 11:14</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>just now</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>EWQEQWASK</t>
+          <t>asdda</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ASBHKDWBK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ID_20260326174009525270</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ASDSADSA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ASFFSAQWE</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-03-26 17:40</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-03-26 17:40</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>THICH GI</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>KHONG THICH GI HET</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ID_20260326174009525270</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ASDSADSA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ASFFSAQWE</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-03-26 17:40</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-03-26 17:40</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>THI THOI</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>THICH THOI KHONG</t>
+          <t>afs</t>
         </is>
       </c>
     </row>
